--- a/artfynd/A 38950-2021 artfynd.xlsx
+++ b/artfynd/A 38950-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38950-2021 artfynd.xlsx
+++ b/artfynd/A 38950-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62589587</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54268151</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819664</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819665</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61001350</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56512393</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819678</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819679</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819680</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819681</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61001349</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73768370</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162467</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162643</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162694</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119163035</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119163204</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,6 +2588,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119164210</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2595,6 +2690,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219127</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2696,6 +2796,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55948748</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2798,6 +2903,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819687</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2895,6 +3005,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162874</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2997,6 +3112,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54268062</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3099,6 +3219,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61001346</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3201,6 +3326,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819667</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3303,6 +3433,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56819688</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3405,6 +3540,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61001348</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3507,6 +3647,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73768368</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,6 +3754,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73768369</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3711,6 +3861,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54268060</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3813,6 +3968,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119162928</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3915,6 +4075,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119163360</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4017,6 +4182,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119165444</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4119,8 +4289,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54268061</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>